--- a/design/usdm/DAS.xlsx
+++ b/design/usdm/DAS.xlsx
@@ -16,11 +16,11 @@
     <sheet name="7.LLMエンジニアリング" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1.プロダクトライン管理'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1.プロダクトライン管理'!$A$1:$E$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.ユーザー管理'!$A$1:$E$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3.開発プロセス管理'!$A$1:$E$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4.成果物・構成管理'!$A$1:$E$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5.製品窓口対応・レポート'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4.成果物・構成管理'!$A$1:$E$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5.製品窓口対応・レポート'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6.システムアーキテクチャ'!$A$1:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'7.LLMエンジニアリング'!$A$1:$E$37</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="397">
   <si>
     <t>カテゴリ名</t>
   </si>
@@ -94,8 +94,7 @@
     <t>【DAS_R01.DM01-04】</t>
   </si>
   <si>
-    <t xml:space="preserve">顧客単位でユーザーのアクセス権限（パーミッション）を設定する
-【補足】書込可能（作成・変更・削除）または閲覧のみを指定できる（ユーザー管理機能と連携する将来的な要求）</t>
+    <t>顧客情報を削除した場合、当該顧客に紐づく製品情報をすべて削除する</t>
   </si>
   <si>
     <t>02</t>
@@ -228,6 +227,12 @@
     <t>登録済みのプラットフォーム情報を削除する</t>
   </si>
   <si>
+    <t>【DAS_R03.DM01-04】</t>
+  </si>
+  <si>
+    <t>プラットフォームを削除した場合、当該プラットフォームに紐づく成果物およびトレーサビリティの情報をすべて削除する</t>
+  </si>
+  <si>
     <t>登録されたプラットフォーム情報を一覧表示し、条件によって検索（フィルタ）する</t>
   </si>
   <si>
@@ -276,7 +281,7 @@
     <t>【DAS_R03.DM04-01】</t>
   </si>
   <si>
-    <t>プラットフォームから派生した個別顧客向けカスタマイズを作成する</t>
+    <t>ベースとして採用するプラットフォームのバージョンから独自の変更（リビジョン）を保持できること</t>
   </si>
   <si>
     <t>【DAS_R03.DM04-02】</t>
@@ -418,7 +423,7 @@
     <t>【DAS_R05.DM03-01】</t>
   </si>
   <si>
-    <t>生成AIが開発プロセス（ワークフロー）の作成・変更を支援する</t>
+    <t>ユーザーからのチャット入力に基づいて、ワークフローの生成・変更を可能とする</t>
   </si>
   <si>
     <t>各開発プロセスにガードレールを設ける</t>
@@ -710,6 +715,45 @@
 【理由】AIが変更理由をたどれるようにするため</t>
   </si>
   <si>
+    <t>バージョンが付与されていない製品について、最新の成果物を取得・変更する</t>
+  </si>
+  <si>
+    <t>リリース前の開発中であっても、最新の成果物を継続して参照・編集できるようにするため</t>
+  </si>
+  <si>
+    <t>【DAS_R11.DM04-01】</t>
+  </si>
+  <si>
+    <t>バージョンが付与されていない製品について、最新の成果物を取得する</t>
+  </si>
+  <si>
+    <t>【DAS_R11.DM04-02】</t>
+  </si>
+  <si>
+    <t>バージョンが付与されていない製品について、最新の成果物を変更する</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>顧客や製品の削除に伴い、いずれの製品の最新成果物または特定のバージョンからも辿れなくなったリビジョンおよびトレーサビリティの情報を削除する</t>
+  </si>
+  <si>
+    <t>データベースの容量肥大化を防ぐため</t>
+  </si>
+  <si>
+    <t>【DAS_R11.DM05-01】</t>
+  </si>
+  <si>
+    <t>顧客または製品の削除後、すべての製品の最新成果物または特定のバージョンのいずれからも参照されないリビジョン情報を削除する</t>
+  </si>
+  <si>
+    <t>【DAS_R11.DM05-02】</t>
+  </si>
+  <si>
+    <t>顧客または製品の削除後、すべての製品の最新成果物または特定のバージョンのいずれからも参照されないトレーサビリティ情報を削除する</t>
+  </si>
+  <si>
     <t>R12</t>
   </si>
   <si>
@@ -915,6 +959,39 @@
   </si>
   <si>
     <t>ユーザーがレポートのテンプレート・内容を編集する</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>ユーザーからチャットでレポートに関する質問が入力されたとき、生成AIが成果物の内容をもとに回答する</t>
+  </si>
+  <si>
+    <t>ユーザーがレポート内容の根拠を成果物に基づいて迅速かつ正確に理解できるようにするため</t>
+  </si>
+  <si>
+    <t>レポートに関するチャットでの質問に対し、成果物の内容をもとに回答を生成する</t>
+  </si>
+  <si>
+    <t>ユーザーがレポートの根拠となる成果物情報を踏まえた正確な回答を得られるようにするため</t>
+  </si>
+  <si>
+    <t>【DAS_R22.DM01-01】</t>
+  </si>
+  <si>
+    <t>ユーザーがチャットでレポートに関する質問を入力する</t>
+  </si>
+  <si>
+    <t>【DAS_R22.DM01-02】</t>
+  </si>
+  <si>
+    <t>生成AIが質問に関連する成果物の内容を参照する</t>
+  </si>
+  <si>
+    <t>【DAS_R22.DM01-03】</t>
+  </si>
+  <si>
+    <t>生成AIが参照した成果物の内容をもとに回答を生成し、チャットの応答として出力する</t>
   </si>
   <si>
     <t>R18</t>
@@ -1617,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2165,28 +2242,30 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" outlineLevel="1">
+    <row r="45" outlineLevel="2">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="8" t="s">
+      <c r="C45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="46" outlineLevel="2">
+      <c r="E45" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="8"/>
+      <c r="C46" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D46" s="7" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" outlineLevel="2">
@@ -2194,23 +2273,21 @@
       <c r="B47" s="6"/>
       <c r="C47" s="8"/>
       <c r="D47" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" outlineLevel="2">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
-      <c r="C48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>68</v>
+      <c r="C48" s="8"/>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="49" outlineLevel="2">
@@ -2226,28 +2303,30 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" outlineLevel="1">
+    <row r="50" outlineLevel="2">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
-      <c r="C50" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E50" s="8" t="s">
+      <c r="C50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="51" outlineLevel="2">
+      <c r="E50" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
-      <c r="C51" s="8"/>
+      <c r="C51" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D51" s="7" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" outlineLevel="2">
@@ -2255,23 +2334,21 @@
       <c r="B52" s="6"/>
       <c r="C52" s="8"/>
       <c r="D52" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" outlineLevel="2">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
-      <c r="C53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>74</v>
+      <c r="C53" s="8"/>
+      <c r="D53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" outlineLevel="2">
@@ -2287,28 +2364,30 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" outlineLevel="1">
+    <row r="55" outlineLevel="2">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
-      <c r="C55" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="7" t="s">
+      <c r="C55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="56" outlineLevel="2">
+    <row r="56" outlineLevel="1">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
-      <c r="C56" s="8"/>
+      <c r="C56" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D56" s="7" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" outlineLevel="2">
@@ -2316,23 +2395,21 @@
       <c r="B57" s="6"/>
       <c r="C57" s="8"/>
       <c r="D57" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" outlineLevel="2">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
-      <c r="C58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>81</v>
+      <c r="C58" s="8"/>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59" outlineLevel="2">
@@ -2348,8 +2425,21 @@
         <v>83</v>
       </c>
     </row>
+    <row r="60" outlineLevel="2">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E59"/>
+  <autoFilter ref="A1:E60"/>
   <mergeCells count="10">
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D1:E1"/>
@@ -2403,10 +2493,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -2417,7 +2507,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -2428,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -2442,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -2453,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -2474,10 +2564,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
@@ -2487,10 +2577,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" outlineLevel="1">
@@ -2503,7 +2593,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" outlineLevel="2">
@@ -2514,7 +2604,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" outlineLevel="2">
@@ -2535,10 +2625,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" outlineLevel="1">
@@ -2551,7 +2641,7 @@
         <v>46</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" outlineLevel="2">
@@ -2562,7 +2652,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" outlineLevel="2">
@@ -2583,10 +2673,10 @@
         <v>13</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" outlineLevel="2">
@@ -2596,10 +2686,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" outlineLevel="2">
@@ -2609,10 +2699,10 @@
         <v>13</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" outlineLevel="2">
@@ -2622,10 +2712,10 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" outlineLevel="2">
@@ -2635,10 +2725,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2690,10 +2780,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -2704,7 +2794,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -2715,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -2729,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -2740,7 +2830,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -2761,10 +2851,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" outlineLevel="1">
@@ -2777,7 +2867,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" outlineLevel="2">
@@ -2788,7 +2878,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" outlineLevel="2">
@@ -2799,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" outlineLevel="2">
@@ -2809,10 +2899,10 @@
         <v>13</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" outlineLevel="2">
@@ -2822,10 +2912,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" outlineLevel="1">
@@ -2838,7 +2928,7 @@
         <v>46</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" outlineLevel="2">
@@ -2849,7 +2939,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" outlineLevel="2">
@@ -2870,10 +2960,10 @@
         <v>13</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" outlineLevel="1">
@@ -2883,10 +2973,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" outlineLevel="2">
@@ -2897,7 +2987,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" outlineLevel="2">
@@ -2918,10 +3008,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -2930,10 +3020,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -2944,7 +3034,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -2969,7 +3059,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" outlineLevel="2">
@@ -2980,7 +3070,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" outlineLevel="2">
@@ -3001,10 +3091,10 @@
         <v>13</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" outlineLevel="2">
@@ -3014,10 +3104,10 @@
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" outlineLevel="1">
@@ -3030,7 +3120,7 @@
         <v>22</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" outlineLevel="2">
@@ -3041,7 +3131,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" outlineLevel="2">
@@ -3062,10 +3152,10 @@
         <v>13</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" outlineLevel="2">
@@ -3075,10 +3165,10 @@
         <v>13</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35">
@@ -3087,10 +3177,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E35" s="5"/>
     </row>
@@ -3101,7 +3191,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E36" s="5"/>
     </row>
@@ -3126,7 +3216,7 @@
         <v>10</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" outlineLevel="2">
@@ -3137,7 +3227,7 @@
         <v>6</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" outlineLevel="2">
@@ -3158,10 +3248,10 @@
         <v>13</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" outlineLevel="1">
@@ -3174,7 +3264,7 @@
         <v>22</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" outlineLevel="2">
@@ -3185,7 +3275,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" outlineLevel="2">
@@ -3206,10 +3296,10 @@
         <v>13</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" outlineLevel="2">
@@ -3219,10 +3309,10 @@
         <v>13</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" outlineLevel="1">
@@ -3235,7 +3325,7 @@
         <v>46</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" outlineLevel="2">
@@ -3246,7 +3336,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" outlineLevel="2">
@@ -3267,10 +3357,10 @@
         <v>13</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51">
@@ -3279,10 +3369,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E51" s="5"/>
     </row>
@@ -3293,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E52" s="5"/>
     </row>
@@ -3318,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" outlineLevel="2">
@@ -3329,7 +3419,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" outlineLevel="2">
@@ -3350,10 +3440,10 @@
         <v>13</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" outlineLevel="1">
@@ -3366,7 +3456,7 @@
         <v>22</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" outlineLevel="2">
@@ -3377,7 +3467,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" outlineLevel="2">
@@ -3398,10 +3488,10 @@
         <v>13</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" outlineLevel="2">
@@ -3411,10 +3501,10 @@
         <v>13</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" outlineLevel="1">
@@ -3427,7 +3517,7 @@
         <v>46</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" outlineLevel="2">
@@ -3438,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" outlineLevel="2">
@@ -3459,10 +3549,10 @@
         <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" outlineLevel="2">
@@ -3472,10 +3562,10 @@
         <v>13</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3505,7 +3595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3536,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -3550,7 +3640,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -3561,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -3575,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -3586,7 +3676,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -3607,10 +3697,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
@@ -3620,10 +3710,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3632,10 +3722,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E10" s="5"/>
     </row>
@@ -3646,7 +3736,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -3671,7 +3761,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" outlineLevel="2">
@@ -3682,7 +3772,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" outlineLevel="2">
@@ -3703,10 +3793,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" outlineLevel="1">
@@ -3719,7 +3809,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" outlineLevel="2">
@@ -3730,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" outlineLevel="2">
@@ -3751,10 +3841,10 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
@@ -3763,10 +3853,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E21" s="5"/>
     </row>
@@ -3777,7 +3867,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -3788,7 +3878,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -3802,7 +3892,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" outlineLevel="2">
@@ -3813,7 +3903,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" outlineLevel="2">
@@ -3834,10 +3924,10 @@
         <v>13</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" outlineLevel="1">
@@ -3850,7 +3940,7 @@
         <v>22</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" outlineLevel="2">
@@ -3861,7 +3951,7 @@
         <v>6</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" outlineLevel="2">
@@ -3882,10 +3972,10 @@
         <v>13</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" outlineLevel="2">
@@ -3895,10 +3985,10 @@
         <v>13</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" outlineLevel="1">
@@ -3911,7 +4001,7 @@
         <v>46</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" outlineLevel="2">
@@ -3922,7 +4012,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" outlineLevel="2">
@@ -3943,10 +4033,10 @@
         <v>13</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" outlineLevel="2">
@@ -3956,250 +4046,250 @@
         <v>13</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="3" t="s">
+    </row>
+    <row r="38" outlineLevel="1">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" outlineLevel="1">
+    </row>
+    <row r="39" outlineLevel="2">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" outlineLevel="2">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" outlineLevel="2">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
-      <c r="C41" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>228</v>
+      <c r="C41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="42" outlineLevel="2">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="43" outlineLevel="2">
+      <c r="C42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
-      <c r="C43" s="8"/>
+      <c r="C43" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D43" s="7" t="s">
-        <v>8</v>
+        <v>233</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>9</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" outlineLevel="2">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
-      <c r="C44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="45" outlineLevel="1">
+      <c r="C44" s="8"/>
+      <c r="D44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="45" outlineLevel="2">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
-      <c r="C45" s="7" t="s">
-        <v>1</v>
-      </c>
+      <c r="C45" s="8"/>
       <c r="D45" s="7" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" outlineLevel="2">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>233</v>
+      <c r="C46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="47" outlineLevel="2">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" outlineLevel="2">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" outlineLevel="2">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="C47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3"/>
+      <c r="B48" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" outlineLevel="1">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" outlineLevel="1">
       <c r="A50" s="3"/>
-      <c r="B50" s="4" t="s">
-        <v>1</v>
-      </c>
+      <c r="B50" s="3"/>
       <c r="C50" s="4" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>239</v>
+        <v>9</v>
       </c>
       <c r="E50" s="5"/>
     </row>
     <row r="51" outlineLevel="1">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E51" s="5"/>
-    </row>
-    <row r="52" outlineLevel="1">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="5"/>
-    </row>
-    <row r="53" outlineLevel="1">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="52" outlineLevel="2">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" outlineLevel="2">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
-      <c r="C53" s="7" t="s">
-        <v>1</v>
-      </c>
+      <c r="C53" s="8"/>
       <c r="D53" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>241</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" outlineLevel="2">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="55" outlineLevel="2">
+      <c r="C54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
-      <c r="C55" s="8"/>
+      <c r="C55" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D55" s="7" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" outlineLevel="2">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
-      <c r="C56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>244</v>
+      <c r="C56" s="8"/>
+      <c r="D56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="57" outlineLevel="2">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
-      <c r="C57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>246</v>
+      <c r="C57" s="8"/>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="58" outlineLevel="2">
@@ -4209,10 +4299,10 @@
         <v>13</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" outlineLevel="2">
@@ -4222,106 +4312,106 @@
         <v>13</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" outlineLevel="2">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E60" s="6" t="s">
         <v>252</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E60" s="5"/>
+    </row>
     <row r="61" outlineLevel="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="62" outlineLevel="2">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="63" outlineLevel="2">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E61" s="5"/>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="5"/>
+    </row>
+    <row r="63" outlineLevel="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
-      <c r="C63" s="8"/>
+      <c r="C63" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D63" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>9</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" outlineLevel="2">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
-      <c r="C64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="65" outlineLevel="1">
+      <c r="C64" s="8"/>
+      <c r="D64" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" outlineLevel="2">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
-      <c r="C65" s="7" t="s">
-        <v>1</v>
-      </c>
+      <c r="C65" s="8"/>
       <c r="D65" s="7" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" outlineLevel="2">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="C66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>258</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="67" outlineLevel="2">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>9</v>
+      <c r="C67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="68" outlineLevel="2">
@@ -4331,89 +4421,211 @@
         <v>13</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="69" outlineLevel="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="69" outlineLevel="2">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
-      <c r="C69" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>261</v>
+      <c r="C69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="70" outlineLevel="2">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="71" outlineLevel="2">
+      <c r="C70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
-      <c r="C71" s="8"/>
+      <c r="C71" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="D71" s="7" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>9</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72" outlineLevel="2">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
-      <c r="C72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>264</v>
+      <c r="C72" s="8"/>
+      <c r="D72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="73" outlineLevel="2">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
-      <c r="C73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>266</v>
+      <c r="C73" s="8"/>
+      <c r="D73" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" outlineLevel="2">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="76" outlineLevel="2">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="77" outlineLevel="2">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" outlineLevel="2">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" outlineLevel="2">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" outlineLevel="2">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" outlineLevel="2">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" outlineLevel="2">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E83"/>
   <mergeCells count="16">
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D60:E60"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D49:E49"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D61:E61"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D62:E62"/>
     <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D21:E21"/>
@@ -4428,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4459,10 +4671,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -4473,7 +4685,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -4498,7 +4710,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -4509,7 +4721,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -4530,10 +4742,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
@@ -4543,10 +4755,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" outlineLevel="2">
@@ -4556,10 +4768,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
@@ -4568,10 +4780,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -4582,7 +4794,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="E12" s="5"/>
     </row>
@@ -4607,7 +4819,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" outlineLevel="2">
@@ -4618,7 +4830,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" outlineLevel="2">
@@ -4639,10 +4851,10 @@
         <v>13</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" outlineLevel="2">
@@ -4652,10 +4864,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19">
@@ -4664,10 +4876,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4678,7 +4890,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="E20" s="5"/>
     </row>
@@ -4703,7 +4915,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" outlineLevel="2">
@@ -4714,7 +4926,7 @@
         <v>6</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" outlineLevel="2">
@@ -4735,22 +4947,134 @@
         <v>13</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>293</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" outlineLevel="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" outlineLevel="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" outlineLevel="2">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" outlineLevel="2">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" outlineLevel="2">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" outlineLevel="2">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" outlineLevel="2">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
-  <mergeCells count="10">
+  <autoFilter ref="A1:E34"/>
+  <mergeCells count="13">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D21:E21"/>
@@ -4796,10 +5120,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -4810,7 +5134,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -4835,7 +5159,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -4846,7 +5170,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -4867,10 +5191,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
@@ -4880,10 +5204,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" outlineLevel="1">
@@ -4896,7 +5220,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" outlineLevel="2">
@@ -4907,7 +5231,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" outlineLevel="2">
@@ -4928,10 +5252,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" outlineLevel="2">
@@ -4941,10 +5265,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15">
@@ -4953,10 +5277,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -4967,7 +5291,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="E16" s="5"/>
     </row>
@@ -4992,7 +5316,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" outlineLevel="2">
@@ -5003,7 +5327,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" outlineLevel="2">
@@ -5024,10 +5348,10 @@
         <v>13</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" outlineLevel="2">
@@ -5037,10 +5361,10 @@
         <v>13</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" outlineLevel="1">
@@ -5053,7 +5377,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" outlineLevel="2">
@@ -5064,7 +5388,7 @@
         <v>6</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" outlineLevel="2">
@@ -5085,10 +5409,10 @@
         <v>13</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27">
@@ -5097,10 +5421,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5"/>
     </row>
@@ -5111,7 +5435,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="E28" s="5"/>
     </row>
@@ -5136,7 +5460,7 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" outlineLevel="2">
@@ -5147,7 +5471,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" outlineLevel="2">
@@ -5168,10 +5492,10 @@
         <v>13</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" outlineLevel="1">
@@ -5184,7 +5508,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" outlineLevel="2">
@@ -5195,7 +5519,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" outlineLevel="2">
@@ -5216,10 +5540,10 @@
         <v>13</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -5277,10 +5601,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -5291,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -5302,7 +5626,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -5316,7 +5640,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -5327,7 +5651,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" outlineLevel="2">
@@ -5348,10 +5672,10 @@
         <v>13</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
@@ -5361,10 +5685,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" outlineLevel="1">
@@ -5377,7 +5701,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" outlineLevel="2">
@@ -5388,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" outlineLevel="2">
@@ -5409,10 +5733,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" outlineLevel="2">
@@ -5422,10 +5746,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" outlineLevel="2">
@@ -5435,10 +5759,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16">
@@ -5447,10 +5771,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="E16" s="5"/>
     </row>
@@ -5461,7 +5785,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -5472,7 +5796,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -5486,7 +5810,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" outlineLevel="2">
@@ -5497,7 +5821,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" outlineLevel="2">
@@ -5518,10 +5842,10 @@
         <v>13</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" outlineLevel="2">
@@ -5531,10 +5855,10 @@
         <v>13</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" outlineLevel="2">
@@ -5544,10 +5868,10 @@
         <v>13</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" outlineLevel="1">
@@ -5560,7 +5884,7 @@
         <v>22</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" outlineLevel="2">
@@ -5571,7 +5895,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" outlineLevel="2">
@@ -5592,10 +5916,10 @@
         <v>13</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" outlineLevel="1">
@@ -5608,7 +5932,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" outlineLevel="2">
@@ -5619,7 +5943,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" outlineLevel="2">
@@ -5640,10 +5964,10 @@
         <v>13</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" outlineLevel="1">
@@ -5653,10 +5977,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" outlineLevel="2">
@@ -5667,7 +5991,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" outlineLevel="2">
@@ -5688,10 +6012,10 @@
         <v>13</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" outlineLevel="2">
@@ -5701,10 +6025,10 @@
         <v>13</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
